--- a/data/packing_engine_normalized_masters_ko_json_schema_fixed.xlsx
+++ b/data/packing_engine_normalized_masters_ko_json_schema_fixed.xlsx
@@ -20473,7 +20473,7 @@
         <v>7.6</v>
       </c>
       <c r="E233" s="39" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="F233" s="39" t="n">
         <v>0.08</v>

--- a/data/packing_engine_normalized_masters_ko_json_schema_fixed.xlsx
+++ b/data/packing_engine_normalized_masters_ko_json_schema_fixed.xlsx
@@ -21391,7 +21391,7 @@
         <v>14</v>
       </c>
       <c r="J5" s="59" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>30</v>
@@ -21445,7 +21445,7 @@
         <v>9.5</v>
       </c>
       <c r="J6" s="59" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>30</v>
@@ -21499,7 +21499,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="59" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>30</v>
@@ -21553,7 +21553,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="59" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>30</v>
@@ -21607,7 +21607,7 @@
         <v>33</v>
       </c>
       <c r="J9" s="59" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>30</v>
@@ -21661,7 +21661,7 @@
         <v>39.5</v>
       </c>
       <c r="J10" s="59" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>30</v>
@@ -21715,7 +21715,7 @@
         <v>39</v>
       </c>
       <c r="J11" s="59" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>30</v>
@@ -21823,7 +21823,7 @@
         <v>39</v>
       </c>
       <c r="J13" s="59" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>30</v>
